--- a/artfynd/A 5530-2025 artfynd.xlsx
+++ b/artfynd/A 5530-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,6 +938,136 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127921880</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56585</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Växjövägen, 302 59 Halmstad, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>373156</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6283621</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Snöstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>

--- a/artfynd/A 5530-2025 artfynd.xlsx
+++ b/artfynd/A 5530-2025 artfynd.xlsx
@@ -948,7 +948,7 @@
         <v>127921880</v>
       </c>
       <c r="B4" t="n">
-        <v>56585</v>
+        <v>56612</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5530-2025 artfynd.xlsx
+++ b/artfynd/A 5530-2025 artfynd.xlsx
@@ -948,7 +948,7 @@
         <v>127921880</v>
       </c>
       <c r="B4" t="n">
-        <v>56612</v>
+        <v>56615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5530-2025 artfynd.xlsx
+++ b/artfynd/A 5530-2025 artfynd.xlsx
@@ -948,7 +948,7 @@
         <v>127921880</v>
       </c>
       <c r="B4" t="n">
-        <v>56615</v>
+        <v>56618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5530-2025 artfynd.xlsx
+++ b/artfynd/A 5530-2025 artfynd.xlsx
@@ -948,7 +948,7 @@
         <v>127921880</v>
       </c>
       <c r="B4" t="n">
-        <v>56618</v>
+        <v>56620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5530-2025 artfynd.xlsx
+++ b/artfynd/A 5530-2025 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119980081</v>
+        <v>119979440</v>
       </c>
       <c r="B2" t="n">
-        <v>56243</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>373354</v>
+        <v>373283</v>
       </c>
       <c r="R2" t="n">
-        <v>6283742</v>
+        <v>6283707</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -769,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,19 +805,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119979440</v>
+        <v>119980081</v>
       </c>
       <c r="B3" t="n">
-        <v>56243</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -869,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>373283</v>
+        <v>373354</v>
       </c>
       <c r="R3" t="n">
-        <v>6283707</v>
+        <v>6283742</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -904,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -914,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -948,11 +938,11 @@
         <v>127921880</v>
       </c>
       <c r="B4" t="n">
-        <v>56620</v>
+        <v>56845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1064,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
+          <t>Via Johan Möller</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 5530-2025 artfynd.xlsx
+++ b/artfynd/A 5530-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119979440</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -932,6 +942,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119980081</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1062,8 +1077,18 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127921880</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>